--- a/artfynd/A 43709-2025 artfynd.xlsx
+++ b/artfynd/A 43709-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80897295</v>
+        <v>137490599</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,49 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännan, Femtibacken, Nb</t>
+          <t>Kvarnberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801428</v>
+        <v>801267</v>
       </c>
       <c r="R5" t="n">
-        <v>7329377</v>
+        <v>7329364</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,22 +1135,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,58 +1155,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Tyr Nilsson, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80897295</t>
+          <t>https://artportalen.se/Sighting/137490599</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88175497</v>
+        <v>80897295</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1268,27 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2019-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2019-11-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I flera brandskadade björkar.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1273,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,6 +1289,133 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80897295</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88175497</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännan, Femtibacken, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>801428</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7329377</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I flera brandskadade björkar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88175497</t>
         </is>
@@ -1326,6 +1428,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43709-2025 artfynd.xlsx
+++ b/artfynd/A 43709-2025 artfynd.xlsx
@@ -1073,7 +1073,7 @@
         <v>137490599</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
